--- a/diseases/d099/2000-2004.xlsx
+++ b/diseases/d099/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>14</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.2704686052117561</v>
       </c>
@@ -1639,9 +1636,6 @@
       <c r="O6" t="n">
         <v>17</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.3785460580328921</v>
       </c>
@@ -2035,9 +2029,6 @@
       <c r="O8" t="n">
         <v>21</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.4057029078176342</v>
       </c>
@@ -2670,9 +2661,6 @@
       <c r="O11" t="n">
         <v>29</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.6457550401737571</v>
       </c>
@@ -3066,9 +3054,6 @@
       <c r="O13" t="n">
         <v>28</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.5409372104235123</v>
       </c>
@@ -3701,9 +3686,6 @@
       <c r="O16" t="n">
         <v>42</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.9352314374930274</v>
       </c>
@@ -4097,9 +4079,6 @@
       <c r="O18" t="n">
         <v>13</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.2511494191252021</v>
       </c>
@@ -4732,9 +4711,6 @@
       <c r="O21" t="n">
         <v>28</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.6234876249953517</v>
       </c>
@@ -5128,9 +5104,6 @@
       <c r="O23" t="n">
         <v>15</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.2897877912983102</v>
       </c>
@@ -5763,9 +5736,6 @@
       <c r="O26" t="n">
         <v>26</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.5789527946385408</v>
       </c>
@@ -6159,9 +6129,6 @@
       <c r="O28" t="n">
         <v>23</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.4443412799907422</v>
       </c>
@@ -6794,9 +6761,6 @@
       <c r="O31" t="n">
         <v>23</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.5121505491033246</v>
       </c>
@@ -7190,9 +7154,6 @@
       <c r="O33" t="n">
         <v>10</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.1931918608655401</v>
       </c>
@@ -7825,9 +7786,6 @@
       <c r="O36" t="n">
         <v>33</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.7348247008873788</v>
       </c>
@@ -8221,9 +8179,6 @@
       <c r="O38" t="n">
         <v>28</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.5409372104235123</v>
       </c>
@@ -8856,9 +8811,6 @@
       <c r="O41" t="n">
         <v>37</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.8238943616010004</v>
       </c>
@@ -9252,9 +9204,6 @@
       <c r="O43" t="n">
         <v>14</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.2704686052117561</v>
       </c>
@@ -9887,9 +9836,6 @@
       <c r="O46" t="n">
         <v>27</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.6012202098169462</v>
       </c>
@@ -10283,9 +10229,6 @@
       <c r="O48" t="n">
         <v>22</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.4250220939041883</v>
       </c>
@@ -10918,9 +10861,6 @@
       <c r="O51" t="n">
         <v>26</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.5789527946385408</v>
       </c>
@@ -11314,9 +11254,6 @@
       <c r="O53" t="n">
         <v>13</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.2511494191252021</v>
       </c>
@@ -11949,9 +11886,6 @@
       <c r="O56" t="n">
         <v>33</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.7348247008873788</v>
       </c>
@@ -12345,9 +12279,6 @@
       <c r="O58" t="n">
         <v>20</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.3863837217310802</v>
       </c>
@@ -12980,9 +12911,6 @@
       <c r="O61" t="n">
         <v>22</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.4898831339249192</v>
       </c>
@@ -13376,9 +13304,6 @@
       <c r="O63" t="n">
         <v>23</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.4433332414541253</v>
       </c>
@@ -14250,9 +14175,6 @@
       <c r="O67" t="n">
         <v>20</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.4430996861303373</v>
       </c>
@@ -14646,9 +14568,6 @@
       <c r="O69" t="n">
         <v>10</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.1927535832409241</v>
       </c>
@@ -15281,9 +15200,6 @@
       <c r="O72" t="n">
         <v>25</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.5538746076629216</v>
       </c>
@@ -15677,9 +15593,6 @@
       <c r="O74" t="n">
         <v>26</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.5011593164264025</v>
       </c>
@@ -16312,9 +16225,6 @@
       <c r="O77" t="n">
         <v>19</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.4209447018238204</v>
       </c>
@@ -16708,9 +16618,6 @@
       <c r="O79" t="n">
         <v>24</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.4626085997782177</v>
       </c>
@@ -17343,9 +17250,6 @@
       <c r="O82" t="n">
         <v>26</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.5760295919694386</v>
       </c>
@@ -17739,9 +17643,6 @@
       <c r="O84" t="n">
         <v>28</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.5397100330745873</v>
       </c>
@@ -18374,9 +18275,6 @@
       <c r="O87" t="n">
         <v>29</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.642494544888989</v>
       </c>
@@ -18770,9 +18668,6 @@
       <c r="O89" t="n">
         <v>30</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.5782607497227721</v>
       </c>
@@ -19405,9 +19300,6 @@
       <c r="O92" t="n">
         <v>36</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.7975794350346073</v>
       </c>
@@ -19801,9 +19693,6 @@
       <c r="O94" t="n">
         <v>26</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.5011593164264025</v>
       </c>
@@ -20436,9 +20325,6 @@
       <c r="O97" t="n">
         <v>26</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.5760295919694386</v>
       </c>
@@ -20832,9 +20718,6 @@
       <c r="O99" t="n">
         <v>22</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.424057883130033</v>
       </c>
@@ -21467,9 +21350,6 @@
       <c r="O102" t="n">
         <v>30</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.664649529195506</v>
       </c>
@@ -21863,9 +21743,6 @@
       <c r="O104" t="n">
         <v>30</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.5782607497227721</v>
       </c>
@@ -22498,9 +22375,6 @@
       <c r="O107" t="n">
         <v>19</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.4209447018238204</v>
       </c>
@@ -22894,9 +22768,6 @@
       <c r="O109" t="n">
         <v>37</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.7131882579914189</v>
       </c>
@@ -23529,9 +23400,6 @@
       <c r="O112" t="n">
         <v>41</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.9083543565671915</v>
       </c>
@@ -23925,9 +23793,6 @@
       <c r="O114" t="n">
         <v>26</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.5011593164264025</v>
       </c>
@@ -24560,9 +24425,6 @@
       <c r="O117" t="n">
         <v>39</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.8640443879541577</v>
       </c>
@@ -24956,9 +24818,6 @@
       <c r="O119" t="n">
         <v>19</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.3662318081577557</v>
       </c>
@@ -25591,9 +25450,6 @@
       <c r="O122" t="n">
         <v>27</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.5981845762759553</v>
       </c>
@@ -25987,9 +25843,6 @@
       <c r="O124" t="n">
         <v>18</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.3461175038159455</v>
       </c>
@@ -26861,9 +26714,6 @@
       <c r="O128" t="n">
         <v>39</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.8594067801465575</v>
       </c>
@@ -27257,9 +27107,6 @@
       <c r="O130" t="n">
         <v>18</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.3461175038159455</v>
       </c>
@@ -27892,9 +27739,6 @@
       <c r="O133" t="n">
         <v>37</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.8153346375749392</v>
       </c>
@@ -28288,9 +28132,6 @@
       <c r="O135" t="n">
         <v>15</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.2884312531799545</v>
       </c>
@@ -28923,9 +28764,6 @@
       <c r="O138" t="n">
         <v>28</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.6170099960026567</v>
       </c>
@@ -29319,9 +29157,6 @@
       <c r="O140" t="n">
         <v>29</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.5576337561479121</v>
       </c>
@@ -29954,9 +29789,6 @@
       <c r="O143" t="n">
         <v>28</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.6170099960026567</v>
       </c>
@@ -30350,9 +30182,6 @@
       <c r="O145" t="n">
         <v>20</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.3845750042399394</v>
       </c>
@@ -30985,9 +30814,6 @@
       <c r="O148" t="n">
         <v>31</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.6831182098600842</v>
       </c>
@@ -31381,9 +31207,6 @@
       <c r="O150" t="n">
         <v>24</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.4614900050879273</v>
       </c>
@@ -32016,9 +31839,6 @@
       <c r="O153" t="n">
         <v>38</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.8373707088607483</v>
       </c>
@@ -32412,9 +32232,6 @@
       <c r="O155" t="n">
         <v>21</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.4038037544519364</v>
       </c>
@@ -33047,9 +32864,6 @@
       <c r="O158" t="n">
         <v>37</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.8153346375749392</v>
       </c>
@@ -33443,9 +33257,6 @@
       <c r="O160" t="n">
         <v>27</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.5191762557239182</v>
       </c>
@@ -34078,9 +33889,6 @@
       <c r="O163" t="n">
         <v>31</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.6831182098600842</v>
       </c>
@@ -34474,9 +34282,6 @@
       <c r="O165" t="n">
         <v>26</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.4999475055119212</v>
       </c>
@@ -35109,9 +34914,6 @@
       <c r="O168" t="n">
         <v>47</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>1.035695350433031</v>
       </c>
@@ -35505,9 +35307,6 @@
       <c r="O170" t="n">
         <v>25</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.4807187552999243</v>
       </c>
@@ -36140,9 +35939,6 @@
       <c r="O173" t="n">
         <v>30</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.661082138574275</v>
       </c>
@@ -36536,9 +36332,6 @@
       <c r="O175" t="n">
         <v>19</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.3653462540279425</v>
       </c>
@@ -37171,9 +36964,6 @@
       <c r="O178" t="n">
         <v>38</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.8373707088607483</v>
       </c>
@@ -37567,9 +37357,6 @@
       <c r="O180" t="n">
         <v>20</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.3845750042399394</v>
       </c>
@@ -38202,9 +37989,6 @@
       <c r="O183" t="n">
         <v>32</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.7051542811458933</v>
       </c>
@@ -38598,9 +38382,6 @@
       <c r="O185" t="n">
         <v>24</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.4603914670278182</v>
       </c>
@@ -39472,9 +39253,6 @@
       <c r="O189" t="n">
         <v>24</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.5257774441038331</v>
       </c>
@@ -39868,9 +39646,6 @@
       <c r="O191" t="n">
         <v>17</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.3261106224780379</v>
       </c>
@@ -40503,9 +40278,6 @@
       <c r="O194" t="n">
         <v>38</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.8324809531644025</v>
       </c>
@@ -40899,9 +40671,6 @@
       <c r="O196" t="n">
         <v>28</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.5371233781991213</v>
       </c>
@@ -41534,9 +41303,6 @@
       <c r="O199" t="n">
         <v>34</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.744851379147097</v>
       </c>
@@ -41930,9 +41696,6 @@
       <c r="O201" t="n">
         <v>30</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.5754893337847727</v>
       </c>
@@ -42565,9 +42328,6 @@
       <c r="O204" t="n">
         <v>45</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.9858327076946872</v>
       </c>
@@ -42961,9 +42721,6 @@
       <c r="O206" t="n">
         <v>28</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.5371233781991213</v>
       </c>
@@ -43596,9 +43353,6 @@
       <c r="O209" t="n">
         <v>28</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.6134070181211387</v>
       </c>
@@ -43992,9 +43746,6 @@
       <c r="O211" t="n">
         <v>26</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.4987574226134697</v>
       </c>
@@ -44627,9 +44378,6 @@
       <c r="O214" t="n">
         <v>25</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.5476848376081596</v>
       </c>
@@ -45023,9 +44771,6 @@
       <c r="O216" t="n">
         <v>26</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.4987574226134697</v>
       </c>
@@ -45658,9 +45403,6 @@
       <c r="O219" t="n">
         <v>17</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.3724256895735485</v>
       </c>
@@ -46054,9 +45796,6 @@
       <c r="O221" t="n">
         <v>24</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.4603914670278182</v>
       </c>
@@ -46689,9 +46428,6 @@
       <c r="O224" t="n">
         <v>18</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.3943330830778749</v>
       </c>
@@ -47085,9 +46821,6 @@
       <c r="O226" t="n">
         <v>23</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.4412084892349924</v>
       </c>
@@ -47720,9 +47453,6 @@
       <c r="O229" t="n">
         <v>31</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.6791291986341178</v>
       </c>
@@ -48116,9 +47846,6 @@
       <c r="O231" t="n">
         <v>29</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.556306355991947</v>
       </c>
@@ -48751,9 +48478,6 @@
       <c r="O234" t="n">
         <v>28</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.6134070181211387</v>
       </c>
@@ -49147,9 +48871,6 @@
       <c r="O236" t="n">
         <v>8</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.1534638223426061</v>
       </c>
@@ -49782,9 +49503,6 @@
       <c r="O239" t="n">
         <v>21</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.460055263590854</v>
       </c>
@@ -50178,9 +49896,6 @@
       <c r="O241" t="n">
         <v>22</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.4220255114421667</v>
       </c>
@@ -50813,9 +50528,6 @@
       <c r="O244" t="n">
         <v>13</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.284796115556243</v>
       </c>
@@ -51209,9 +50921,6 @@
       <c r="O246" t="n">
         <v>19</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.3634174089945426</v>
       </c>
@@ -52083,9 +51792,6 @@
       <c r="O250" t="n">
         <v>27</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.5880120673143148</v>
       </c>
@@ -52479,9 +52185,6 @@
       <c r="O252" t="n">
         <v>22</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.4207991051515756</v>
       </c>
@@ -53114,9 +52817,6 @@
       <c r="O255" t="n">
         <v>31</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.6751249661756947</v>
       </c>
@@ -53510,9 +53210,6 @@
       <c r="O257" t="n">
         <v>35</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.6694531218320522</v>
       </c>
@@ -54145,9 +53842,6 @@
       <c r="O260" t="n">
         <v>44</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.9582418874751797</v>
       </c>
@@ -54541,9 +54235,6 @@
       <c r="O262" t="n">
         <v>26</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.497308033360953</v>
       </c>
@@ -55176,9 +54867,6 @@
       <c r="O265" t="n">
         <v>25</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.5444556178836248</v>
       </c>
@@ -55572,9 +55260,6 @@
       <c r="O267" t="n">
         <v>28</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.5355624974656418</v>
       </c>
@@ -56207,9 +55892,6 @@
       <c r="O270" t="n">
         <v>24</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.5226773931682798</v>
       </c>
@@ -56603,9 +56285,6 @@
       <c r="O272" t="n">
         <v>28</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0.5355624974656418</v>
       </c>
@@ -57238,9 +56917,6 @@
       <c r="O275" t="n">
         <v>25</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.5444556178836248</v>
       </c>
@@ -57634,9 +57310,6 @@
       <c r="O277" t="n">
         <v>30</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.5738169615703305</v>
       </c>
@@ -58269,9 +57942,6 @@
       <c r="O280" t="n">
         <v>28</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.6097902920296598</v>
       </c>
@@ -58665,9 +58335,6 @@
       <c r="O282" t="n">
         <v>18</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.3442901769421983</v>
       </c>
@@ -59300,9 +58967,6 @@
       <c r="O285" t="n">
         <v>28</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.6097902920296598</v>
       </c>
@@ -59696,9 +59360,6 @@
       <c r="O287" t="n">
         <v>17</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.3251629448898539</v>
       </c>
@@ -60331,9 +59992,6 @@
       <c r="O290" t="n">
         <v>30</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.6533467414603498</v>
       </c>
@@ -60727,9 +60385,6 @@
       <c r="O292" t="n">
         <v>19</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.3634174089945426</v>
       </c>
@@ -61362,9 +61017,6 @@
       <c r="O295" t="n">
         <v>62</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>1.350249932351389</v>
       </c>
@@ -61758,9 +61410,6 @@
       <c r="O297" t="n">
         <v>22</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.4207991051515756</v>
       </c>
@@ -62393,9 +62042,6 @@
       <c r="O300" t="n">
         <v>1053</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>22.93247062525828</v>
       </c>
@@ -62789,9 +62435,6 @@
       <c r="O302" t="n">
         <v>16</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.3060357128375096</v>
       </c>
@@ -63423,9 +63066,6 @@
       </c>
       <c r="O305" t="n">
         <v>203</v>
-      </c>
-      <c r="Q305" t="n">
-        <v>0</v>
       </c>
       <c r="R305" t="n">
         <v>4.420979617215034</v>
